--- a/feedback_surveys/019_gym_equipment_usability_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/019_gym_equipment_usability_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Departmental</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Departmental</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Availability Days</t>
+          <t>Availability Days Departmental</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Shift Departmental</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Departmental Comments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Departmental Contact Person</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Departmental Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Departmental Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>departmental_comments</t>
+          <t>departmental_comments_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Departmental Comments 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1169,29 +1169,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>free_weight_machines</t>
+          <t>free_strength_machines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Free Weight Machines</t>
+          <t>Free Strength Machines</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>equipment_availability_choices</t>
+          <t>availability_days_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>free_strength_machines</t>
+          <t>mon-fri</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Free Strength Machines</t>
+          <t>Mon-Fri</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mon-fri</t>
+          <t>mon-thu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mon-Fri</t>
+          <t>Mon-Thu</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mon-thu</t>
+          <t>sat-sun</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mon-Thu</t>
+          <t>Sat-Sun</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sat-sun</t>
+          <t>mon-sat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat-Sun</t>
+          <t>Mon-Sat</t>
         </is>
       </c>
     </row>
@@ -1254,46 +1254,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mon-sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mon-Sat</t>
+          <t>Sun</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>availability_days_choices</t>
+          <t>availability_hours_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mon-thu</t>
+          <t>7am-6pm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mon-Thu</t>
+          <t>7am-6pm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>availability_days_choices</t>
+          <t>availability_hours_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>7am-5pm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>7am-5pm</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7am-6pm</t>
+          <t>8am-6pm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7am-6pm</t>
+          <t>8am-6pm</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7am-5pm</t>
+          <t>8am-5pm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7am-5pm</t>
+          <t>8am-5pm</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8am-6pm</t>
+          <t>6am-6pm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8am-6pm</t>
+          <t>6am-6pm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>availability_hours_choices</t>
+          <t>availability_days_departmental_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8am-5pm</t>
+          <t>mon-fri</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8am-5pm</t>
+          <t>Mon-Fri</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>availability_hours_choices</t>
+          <t>availability_days_departmental_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6am-6pm</t>
+          <t>mon-thu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6am-6pm</t>
+          <t>Mon-Thu</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mon-fri</t>
+          <t>sat-sun</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mon-Fri</t>
+          <t>Sat-Sun</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mon-thu</t>
+          <t>mon-sat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mon-Thu</t>
+          <t>Mon-Sat</t>
         </is>
       </c>
     </row>
@@ -1424,61 +1424,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sat-sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Sat-Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>availability_days_departmental_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mon-sat</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mon-Sat</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>availability_days_departmental_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mon-thu</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Mon-Thu</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>availability_days_departmental_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
